--- a/nr-add-ipp-info/ig/StructureDefinition-fr-core-organization-activity-type.xlsx
+++ b/nr-add-ipp-info/ig/StructureDefinition-fr-core-organization-activity-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T08:40:32+00:00</t>
+    <t>2024-07-22T08:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
